--- a/docs/Budget_sheet_template.xlsx
+++ b/docs/Budget_sheet_template.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="17" min="1" max="1"/>
@@ -580,17 +580,13 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="21" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>proposed</t>
-        </is>
-      </c>
+          <t>Income recognition</t>
+        </is>
+      </c>
+      <c r="B7" s="22"/>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>secured | proposed | archived - must agree with the folder</t>
+          <t>as spent for a grant paid upfront and released as it is spent; blank or as invoiced otherwise</t>
         </is>
       </c>
     </row>
@@ -674,143 +670,173 @@
     <row r="13" ht="15" customHeight="1" s="18">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>victor@wildlife.ai</t>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Health findings for this sheet are addressed here</t>
+          <t>0 to 100, proposed only: the chance this ask is won</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="18">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>Last reviewed</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>46245</v>
-      </c>
+          <t>Exclusivity group</t>
+        </is>
+      </c>
+      <c r="B14" s="23"/>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Date last checked against reality</t>
+          <t>A label shared by competing applications for the same work</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="18">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/EXAMPLE</t>
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>owner@example.org</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Health findings for this sheet are addressed here</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="18">
       <c r="A16" s="21" t="inlineStr">
         <is>
+          <t>Last reviewed</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Date last checked against reality</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="18">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/EXAMPLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Free text. Never put a number here that anything else needs</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Amount requested</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B19" s="27">
         <f>SUM(Budget!E:E)</f>
         <v/>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Derived: total Income on the Budget tab</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="18"/>
-    <row r="19" ht="15" customHeight="1" s="18">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Derived from the Budget tab - do not edit</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="18">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>Total cost</t>
-        </is>
-      </c>
-      <c r="B20" s="27">
-        <f>SUM(Budget!D:D)</f>
-        <v/>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>Sum of the Cost column</t>
-        </is>
-      </c>
-    </row>
+    <row r="20" ht="15" customHeight="1" s="18"/>
     <row r="21" ht="15" customHeight="1" s="18">
       <c r="A21" s="21" t="inlineStr">
         <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B21" s="27">
-        <f>SUM(Budget!E:E)</f>
-        <v/>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>Sum of the Income column</t>
+          <t>Derived from the Budget tab - do not edit</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="18">
       <c r="A22" s="21" t="inlineStr">
         <is>
+          <t>Total cost</t>
+        </is>
+      </c>
+      <c r="B22" s="27">
+        <f>SUM(Budget!D:D)</f>
+        <v/>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Sum of the Cost column</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="18">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B23" s="27">
+        <f>SUM(Budget!E:E)</f>
+        <v/>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Sum of the Income column</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="18">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
           <t>Total contribution</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B24" s="27">
         <f>SUM(Budget!F:F)</f>
         <v/>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>Income minus Cost, per line</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Contribution as % of income</t>
         </is>
       </c>
-      <c r="B23" s="28">
-        <f>IFERROR(B22/B21,0)</f>
-        <v/>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="B25" s="28">
+        <f>IFERROR(B24/B23,0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>Should match the Contribution policy above</t>
         </is>
@@ -822,7 +848,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
-      <formula1>"secured,proposed,archived"</formula1>
+      <formula1>"as spent,as invoiced"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
